--- a/plate3d/PLATE3D_COLNODE.xlsx
+++ b/plate3d/PLATE3D_COLNODE.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="212">
   <si>
     <t>COLUMN NODE</t>
   </si>
@@ -454,6 +454,30 @@
   </si>
   <si>
     <t>the beam start: on the column face, or an end plate further out</t>
+  </si>
+  <si>
+    <t>VIEW</t>
+  </si>
+  <si>
+    <t>ISO</t>
+  </si>
+  <si>
+    <t>COLNODE - ISOMETRIC</t>
+  </si>
+  <si>
+    <t>PLOT</t>
+  </si>
+  <si>
+    <t>PART</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>PLATES</t>
+  </si>
+  <si>
+    <t>SECTIONS</t>
   </si>
   <si>
     <t>END</t>
@@ -1833,13 +1857,13 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T79"/>
+  <dimension ref="A1:T82"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
@@ -1849,17 +1873,17 @@
     <col min="5" max="5" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" s="15" t="s">
         <v>80</v>
       </c>
@@ -1867,12 +1891,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>83</v>
       </c>
@@ -1931,7 +1955,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B7" s="15" t="s">
         <v>85</v>
       </c>
@@ -1982,7 +2006,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B8" s="15" t="s">
         <v>85</v>
       </c>
@@ -2086,12 +2110,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>93</v>
       </c>
@@ -2195,12 +2219,12 @@
         <v>420</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>102</v>
       </c>
@@ -2319,17 +2343,17 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
         <v>110</v>
       </c>
@@ -2371,7 +2395,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>112</v>
       </c>
@@ -2388,7 +2412,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>112</v>
       </c>
@@ -2422,7 +2446,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>112</v>
       </c>
@@ -2439,7 +2463,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>112</v>
       </c>
@@ -2473,7 +2497,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>112</v>
       </c>
@@ -2490,12 +2514,12 @@
         <v>87</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
         <v>118</v>
       </c>
@@ -2551,9 +2575,8 @@
       <c r="C32" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="D32" s="16" t="str">
+      <c r="D32" s="16">
         <f>IF(PARAM!$C$17="fin plate","pl.fin","")</f>
-        <v/>
       </c>
       <c r="E32" s="16" t="s">
         <v>87</v>
@@ -2688,7 +2711,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>112</v>
       </c>
@@ -2705,12 +2728,12 @@
         <v>87</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>126</v>
       </c>
@@ -2725,9 +2748,8 @@
       <c r="C38" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="D38" s="16" t="str">
+      <c r="D38" s="16">
         <f>IF(PARAM!$E$17="end plate","pl.ep","")</f>
-        <v/>
       </c>
       <c r="E38" s="16" t="s">
         <v>87</v>
@@ -2903,7 +2925,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>112</v>
       </c>
@@ -2920,12 +2942,12 @@
         <v>87</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
         <v>128</v>
       </c>
@@ -2940,9 +2962,8 @@
       <c r="C45" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="D45" s="16" t="str">
+      <c r="D45" s="16">
         <f>IF(PARAM!$G$17="end plate","pl.ep","")</f>
-        <v/>
       </c>
       <c r="E45" s="16" t="s">
         <v>87</v>
@@ -3118,7 +3139,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>112</v>
       </c>
@@ -3135,12 +3156,12 @@
         <v>87</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>130</v>
       </c>
@@ -3196,9 +3217,8 @@
       <c r="C53" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="D53" s="16" t="str">
+      <c r="D53" s="16">
         <f>IF(PARAM!$I$17="fin plate","pl.fin","")</f>
-        <v/>
       </c>
       <c r="E53" s="16" t="s">
         <v>87</v>
@@ -3333,7 +3353,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>112</v>
       </c>
@@ -3350,12 +3370,12 @@
         <v>87</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
         <v>132</v>
       </c>
@@ -3390,7 +3410,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="60" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>112</v>
       </c>
@@ -3484,7 +3504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>112</v>
       </c>
@@ -3501,7 +3521,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="63" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>112</v>
       </c>
@@ -3528,7 +3548,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="64" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>112</v>
       </c>
@@ -3556,7 +3576,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
         <v>112</v>
       </c>
@@ -3619,7 +3639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
         <v>112</v>
       </c>
@@ -3636,12 +3656,12 @@
         <v>87</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
         <v>138</v>
       </c>
@@ -3754,7 +3774,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="73" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B73" s="15" t="s">
         <v>140</v>
       </c>
@@ -3805,7 +3825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B75" s="15" t="s">
         <v>140</v>
       </c>
@@ -3829,7 +3849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B76" s="15" t="s">
         <v>140</v>
       </c>
@@ -3853,7 +3873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B77" s="15" t="s">
         <v>140</v>
       </c>
@@ -3877,19 +3897,70 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="10" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B79" s="15" t="s">
+    <row r="79" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B79" t="s">
         <v>147</v>
+      </c>
+      <c r="C79" t="s">
+        <v>141</v>
+      </c>
+      <c r="D79" t="s">
+        <v>148</v>
+      </c>
+      <c r="G79">
+        <v>50</v>
+      </c>
+      <c r="H79" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="80" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B80" t="s">
+        <v>150</v>
+      </c>
+      <c r="C80" t="s">
+        <v>151</v>
+      </c>
+      <c r="D80" t="s">
+        <v>152</v>
+      </c>
+      <c r="E80">
+        <v>10</v>
+      </c>
+      <c r="F80" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="81" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B81" t="s">
+        <v>150</v>
+      </c>
+      <c r="C81" t="s">
+        <v>85</v>
+      </c>
+      <c r="D81" t="s">
+        <v>152</v>
+      </c>
+      <c r="E81">
+        <v>20</v>
+      </c>
+      <c r="F81" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B82" s="15" t="s">
+        <v>155</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -3926,7 +3997,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="B2" s="20">
         <v>100</v>
@@ -3949,7 +4020,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B3" s="22">
         <v>125</v>
@@ -3972,7 +4043,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="B4" s="20">
         <v>150</v>
@@ -3995,7 +4066,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="21" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B5" s="22">
         <v>148</v>
@@ -4018,7 +4089,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="B6" s="20">
         <v>150</v>
@@ -4041,7 +4112,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="21" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="B7" s="22">
         <v>198</v>
@@ -4064,7 +4135,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B8" s="20">
         <v>200</v>
@@ -4087,7 +4158,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="B9" s="22">
         <v>194</v>
@@ -4110,7 +4181,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="B10" s="20">
         <v>200</v>
@@ -4133,7 +4204,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="21" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="B11" s="22">
         <v>200</v>
@@ -4156,7 +4227,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="B12" s="20">
         <v>248</v>
@@ -4179,7 +4250,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="21" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="B13" s="22">
         <v>250</v>
@@ -4202,7 +4273,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B14" s="20">
         <v>244</v>
@@ -4225,7 +4296,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="21" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B15" s="22">
         <v>250</v>
@@ -4248,7 +4319,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="B16" s="20">
         <v>250</v>
@@ -4271,7 +4342,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="21" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B17" s="22">
         <v>298</v>
@@ -4317,7 +4388,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="21" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="B19" s="22">
         <v>294</v>
@@ -4340,7 +4411,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="B20" s="20">
         <v>294</v>
@@ -4386,7 +4457,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="B22" s="20">
         <v>300</v>
@@ -4409,7 +4480,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="21" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="B23" s="22">
         <v>346</v>
@@ -4432,7 +4503,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="B24" s="20">
         <v>350</v>
@@ -4455,7 +4526,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="21" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B25" s="22">
         <v>340</v>
@@ -4478,7 +4549,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="19" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B26" s="20">
         <v>344</v>
@@ -4501,7 +4572,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="21" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B27" s="22">
         <v>350</v>
@@ -4524,7 +4595,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="19" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="B28" s="20">
         <v>396</v>
@@ -4547,7 +4618,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="21" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="B29" s="22">
         <v>400</v>
@@ -4570,7 +4641,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="B30" s="20">
         <v>390</v>
@@ -4593,7 +4664,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="21" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="B31" s="22">
         <v>388</v>
@@ -4616,7 +4687,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B32" s="20">
         <v>394</v>
@@ -4639,7 +4710,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="21" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="B33" s="22">
         <v>400</v>
@@ -4662,7 +4733,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="19" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B34" s="20">
         <v>400</v>
@@ -4685,7 +4756,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="21" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="B35" s="22">
         <v>414</v>
@@ -4708,7 +4779,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="B36" s="20">
         <v>428</v>
@@ -4731,7 +4802,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="21" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="B37" s="22">
         <v>458</v>
@@ -4754,7 +4825,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="B38" s="20">
         <v>498</v>
@@ -4777,7 +4848,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B39" s="22">
         <v>446</v>
@@ -4800,7 +4871,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B40" s="20">
         <v>450</v>
@@ -4823,7 +4894,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="21" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B41" s="22">
         <v>440</v>
@@ -4846,7 +4917,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B42" s="20">
         <v>440</v>
@@ -4869,7 +4940,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="21" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="B43" s="22">
         <v>496</v>
@@ -4892,7 +4963,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="19" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="B44" s="20">
         <v>500</v>
@@ -4915,7 +4986,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="21" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="B45" s="22">
         <v>482</v>
@@ -4938,7 +5009,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="19" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="B46" s="20">
         <v>488</v>
@@ -4961,7 +5032,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="21" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B47" s="22">
         <v>596</v>
@@ -4984,7 +5055,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="19" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="B48" s="20">
         <v>600</v>
@@ -5007,7 +5078,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="21" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="B49" s="22">
         <v>582</v>
@@ -5030,7 +5101,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="19" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="B50" s="20">
         <v>588</v>
@@ -5053,7 +5124,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="21" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B51" s="22">
         <v>594</v>
@@ -5076,7 +5147,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="19" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B52" s="20">
         <v>692</v>
@@ -5099,7 +5170,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="21" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="B53" s="22">
         <v>700</v>
@@ -5122,7 +5193,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="19" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="B54" s="20">
         <v>792</v>
@@ -5145,7 +5216,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="21" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B55" s="22">
         <v>800</v>
@@ -5168,7 +5239,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="19" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="B56" s="20">
         <v>890</v>
@@ -5191,7 +5262,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="21" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="B57" s="22">
         <v>900</v>
@@ -5214,7 +5285,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="19" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B58" s="20">
         <v>912</v>
@@ -5237,7 +5308,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="21" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="B59" s="22">
         <v>918</v>
@@ -5260,6 +5331,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/plate3d/PLATE3D_COLNODE.xlsx
+++ b/plate3d/PLATE3D_COLNODE.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="204">
   <si>
     <t>COLUMN NODE</t>
   </si>
@@ -454,30 +454,6 @@
   </si>
   <si>
     <t>the beam start: on the column face, or an end plate further out</t>
-  </si>
-  <si>
-    <t>VIEW</t>
-  </si>
-  <si>
-    <t>ISO</t>
-  </si>
-  <si>
-    <t>COLNODE - ISOMETRIC</t>
-  </si>
-  <si>
-    <t>PLOT</t>
-  </si>
-  <si>
-    <t>PART</t>
-  </si>
-  <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>PLATES</t>
-  </si>
-  <si>
-    <t>SECTIONS</t>
   </si>
   <si>
     <t>END</t>
@@ -1857,13 +1833,13 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T82"/>
+  <dimension ref="A1:T79"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
@@ -1873,17 +1849,17 @@
     <col min="5" max="5" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="15" t="s">
         <v>80</v>
       </c>
@@ -1891,12 +1867,12 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>83</v>
       </c>
@@ -1955,7 +1931,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B7" s="15" t="s">
         <v>85</v>
       </c>
@@ -2006,7 +1982,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B8" s="15" t="s">
         <v>85</v>
       </c>
@@ -2110,12 +2086,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>93</v>
       </c>
@@ -2219,12 +2195,12 @@
         <v>420</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>102</v>
       </c>
@@ -2343,17 +2319,17 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
         <v>110</v>
       </c>
@@ -2395,7 +2371,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>112</v>
       </c>
@@ -2412,7 +2388,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>112</v>
       </c>
@@ -2446,7 +2422,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>112</v>
       </c>
@@ -2463,7 +2439,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>112</v>
       </c>
@@ -2497,7 +2473,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>112</v>
       </c>
@@ -2514,12 +2490,12 @@
         <v>87</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
         <v>118</v>
       </c>
@@ -2575,8 +2551,9 @@
       <c r="C32" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="D32" s="16">
+      <c r="D32" s="16" t="str">
         <f>IF(PARAM!$C$17="fin plate","pl.fin","")</f>
+        <v/>
       </c>
       <c r="E32" s="16" t="s">
         <v>87</v>
@@ -2711,7 +2688,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>112</v>
       </c>
@@ -2728,12 +2705,12 @@
         <v>87</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>126</v>
       </c>
@@ -2748,8 +2725,9 @@
       <c r="C38" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="D38" s="16">
+      <c r="D38" s="16" t="str">
         <f>IF(PARAM!$E$17="end plate","pl.ep","")</f>
+        <v/>
       </c>
       <c r="E38" s="16" t="s">
         <v>87</v>
@@ -2925,7 +2903,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>112</v>
       </c>
@@ -2942,12 +2920,12 @@
         <v>87</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
         <v>128</v>
       </c>
@@ -2962,8 +2940,9 @@
       <c r="C45" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="D45" s="16">
+      <c r="D45" s="16" t="str">
         <f>IF(PARAM!$G$17="end plate","pl.ep","")</f>
+        <v/>
       </c>
       <c r="E45" s="16" t="s">
         <v>87</v>
@@ -3139,7 +3118,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>112</v>
       </c>
@@ -3156,12 +3135,12 @@
         <v>87</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>130</v>
       </c>
@@ -3217,8 +3196,9 @@
       <c r="C53" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="D53" s="16">
+      <c r="D53" s="16" t="str">
         <f>IF(PARAM!$I$17="fin plate","pl.fin","")</f>
+        <v/>
       </c>
       <c r="E53" s="16" t="s">
         <v>87</v>
@@ -3353,7 +3333,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>112</v>
       </c>
@@ -3370,12 +3350,12 @@
         <v>87</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
         <v>132</v>
       </c>
@@ -3410,7 +3390,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>112</v>
       </c>
@@ -3504,7 +3484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>112</v>
       </c>
@@ -3521,7 +3501,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>112</v>
       </c>
@@ -3548,7 +3528,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>112</v>
       </c>
@@ -3576,7 +3556,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
         <v>112</v>
       </c>
@@ -3639,7 +3619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
         <v>112</v>
       </c>
@@ -3656,12 +3636,12 @@
         <v>87</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
         <v>138</v>
       </c>
@@ -3774,7 +3754,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B73" s="15" t="s">
         <v>140</v>
       </c>
@@ -3825,7 +3805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B75" s="15" t="s">
         <v>140</v>
       </c>
@@ -3849,7 +3829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B76" s="15" t="s">
         <v>140</v>
       </c>
@@ -3873,7 +3853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B77" s="15" t="s">
         <v>140</v>
       </c>
@@ -3897,70 +3877,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="10" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="79" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B79" t="s">
+    <row r="79" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B79" s="15" t="s">
         <v>147</v>
-      </c>
-      <c r="C79" t="s">
-        <v>141</v>
-      </c>
-      <c r="D79" t="s">
-        <v>148</v>
-      </c>
-      <c r="G79">
-        <v>50</v>
-      </c>
-      <c r="H79" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B80" t="s">
-        <v>150</v>
-      </c>
-      <c r="C80" t="s">
-        <v>151</v>
-      </c>
-      <c r="D80" t="s">
-        <v>152</v>
-      </c>
-      <c r="E80">
-        <v>10</v>
-      </c>
-      <c r="F80" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B81" t="s">
-        <v>150</v>
-      </c>
-      <c r="C81" t="s">
-        <v>85</v>
-      </c>
-      <c r="D81" t="s">
-        <v>152</v>
-      </c>
-      <c r="E81">
-        <v>20</v>
-      </c>
-      <c r="F81" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B82" s="15" t="s">
-        <v>155</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -3997,7 +3926,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="B2" s="20">
         <v>100</v>
@@ -4020,7 +3949,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="B3" s="22">
         <v>125</v>
@@ -4043,7 +3972,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="B4" s="20">
         <v>150</v>
@@ -4066,7 +3995,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="21" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="B5" s="22">
         <v>148</v>
@@ -4089,7 +4018,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="B6" s="20">
         <v>150</v>
@@ -4112,7 +4041,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="21" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="B7" s="22">
         <v>198</v>
@@ -4135,7 +4064,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="B8" s="20">
         <v>200</v>
@@ -4158,7 +4087,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="B9" s="22">
         <v>194</v>
@@ -4181,7 +4110,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="B10" s="20">
         <v>200</v>
@@ -4204,7 +4133,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="21" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="B11" s="22">
         <v>200</v>
@@ -4227,7 +4156,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="B12" s="20">
         <v>248</v>
@@ -4250,7 +4179,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="21" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="B13" s="22">
         <v>250</v>
@@ -4273,7 +4202,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="B14" s="20">
         <v>244</v>
@@ -4296,7 +4225,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="21" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="B15" s="22">
         <v>250</v>
@@ -4319,7 +4248,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="B16" s="20">
         <v>250</v>
@@ -4342,7 +4271,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="21" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B17" s="22">
         <v>298</v>
@@ -4388,7 +4317,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="21" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="B19" s="22">
         <v>294</v>
@@ -4411,7 +4340,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="B20" s="20">
         <v>294</v>
@@ -4457,7 +4386,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="B22" s="20">
         <v>300</v>
@@ -4480,7 +4409,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="21" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="B23" s="22">
         <v>346</v>
@@ -4503,7 +4432,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="B24" s="20">
         <v>350</v>
@@ -4526,7 +4455,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="21" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="B25" s="22">
         <v>340</v>
@@ -4549,7 +4478,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="19" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="B26" s="20">
         <v>344</v>
@@ -4572,7 +4501,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="21" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="B27" s="22">
         <v>350</v>
@@ -4595,7 +4524,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="19" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="B28" s="20">
         <v>396</v>
@@ -4618,7 +4547,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="21" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B29" s="22">
         <v>400</v>
@@ -4641,7 +4570,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="B30" s="20">
         <v>390</v>
@@ -4664,7 +4593,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="21" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="B31" s="22">
         <v>388</v>
@@ -4687,7 +4616,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="B32" s="20">
         <v>394</v>
@@ -4710,7 +4639,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="21" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="B33" s="22">
         <v>400</v>
@@ -4733,7 +4662,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="19" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="B34" s="20">
         <v>400</v>
@@ -4756,7 +4685,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="21" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="B35" s="22">
         <v>414</v>
@@ -4779,7 +4708,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="B36" s="20">
         <v>428</v>
@@ -4802,7 +4731,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="21" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="B37" s="22">
         <v>458</v>
@@ -4825,7 +4754,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="B38" s="20">
         <v>498</v>
@@ -4848,7 +4777,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="B39" s="22">
         <v>446</v>
@@ -4871,7 +4800,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="B40" s="20">
         <v>450</v>
@@ -4894,7 +4823,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="21" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="B41" s="22">
         <v>440</v>
@@ -4917,7 +4846,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="B42" s="20">
         <v>440</v>
@@ -4940,7 +4869,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="21" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="B43" s="22">
         <v>496</v>
@@ -4963,7 +4892,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="19" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="B44" s="20">
         <v>500</v>
@@ -4986,7 +4915,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="21" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="B45" s="22">
         <v>482</v>
@@ -5009,7 +4938,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="19" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="B46" s="20">
         <v>488</v>
@@ -5032,7 +4961,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="21" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="B47" s="22">
         <v>596</v>
@@ -5055,7 +4984,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="19" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="B48" s="20">
         <v>600</v>
@@ -5078,7 +5007,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="21" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B49" s="22">
         <v>582</v>
@@ -5101,7 +5030,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="19" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B50" s="20">
         <v>588</v>
@@ -5124,7 +5053,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="21" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B51" s="22">
         <v>594</v>
@@ -5147,7 +5076,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="19" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B52" s="20">
         <v>692</v>
@@ -5170,7 +5099,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="21" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="B53" s="22">
         <v>700</v>
@@ -5193,7 +5122,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="19" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="B54" s="20">
         <v>792</v>
@@ -5216,7 +5145,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="21" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B55" s="22">
         <v>800</v>
@@ -5239,7 +5168,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="19" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="B56" s="20">
         <v>890</v>
@@ -5262,7 +5191,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="21" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B57" s="22">
         <v>900</v>
@@ -5285,7 +5214,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="19" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B58" s="20">
         <v>912</v>
@@ -5308,7 +5237,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="21" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B59" s="22">
         <v>918</v>
@@ -5331,6 +5260,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>